--- a/results/DR_results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/mrt_cp_table.xlsx
+++ b/results/DR_results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/mrt_cp_table.xlsx
@@ -479,16 +479,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9909090909090909</v>
+        <v>0.9818181818181818</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02858782161229272</v>
+        <v>0.04453617714151231</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8386363636363636</v>
+        <v>0.8363636363636364</v>
       </c>
       <c r="H2" t="n">
-        <v>1.090909090909091</v>
+        <v>1.081818181818182</v>
       </c>
     </row>
     <row r="3">
@@ -505,16 +505,16 @@
         <v>0.6363636363636364</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9909090909090909</v>
+        <v>0.9818181818181818</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02858782161229272</v>
+        <v>0.04453617714151231</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8386363636363636</v>
+        <v>0.8363636363636364</v>
       </c>
       <c r="H3" t="n">
-        <v>1.090909090909091</v>
+        <v>1.081818181818182</v>
       </c>
     </row>
     <row r="4">
@@ -531,13 +531,13 @@
         <v>0.3636363636363636</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8363636363636363</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04453617714151232</v>
+        <v>0.07041787902195304</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6636363636363636</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -557,13 +557,13 @@
         <v>0.1818181818181818</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04535342286998716</v>
+        <v>0.07041787902195304</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6636363636363636</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -583,13 +583,13 @@
         <v>0.1818181818181818</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04535342286998716</v>
+        <v>0.07041787902195304</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6636363636363636</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -609,13 +609,13 @@
         <v>0.1818181818181818</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04535342286998716</v>
+        <v>0.07041787902195304</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6636363636363636</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
